--- a/data/industry/CFM/Flash Card.xlsx
+++ b/data/industry/CFM/Flash Card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE43DCD-4D60-4B5C-88AF-12DAED2B0118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242E51EE-9532-45AF-ADFA-0133600BAE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" tabRatio="767" xr2:uid="{9A28822D-BA55-F242-829D-3FA5BE3F147C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="767" xr2:uid="{9A28822D-BA55-F242-829D-3FA5BE3F147C}"/>
   </bookViews>
   <sheets>
     <sheet name="MicroSD 16GB(Channel)" sheetId="1" r:id="rId1"/>
@@ -38,15 +38,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -751,6 +748,36 @@
                 <c:pt idx="167">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="168">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1263,6 +1290,36 @@
                 </c:pt>
                 <c:pt idx="167">
                   <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1790,6 +1847,48 @@
                 <c:pt idx="163">
                   <c:v>6.7</c:v>
                 </c:pt>
+                <c:pt idx="164">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2316,6 +2415,48 @@
                 <c:pt idx="163">
                   <c:v>10</c:v>
                 </c:pt>
+                <c:pt idx="164">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>8.6999999999999993</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2841,6 +2982,48 @@
                 </c:pt>
                 <c:pt idx="163">
                   <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>18.2</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>18.2</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>17.7</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>16.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3016,6 +3199,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3023,7 +3207,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3367,6 +3550,36 @@
                 <c:pt idx="89">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="90">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3633,6 +3846,48 @@
                 </c:pt>
                 <c:pt idx="85">
                   <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>36.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3808,6 +4063,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3815,7 +4071,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4159,6 +4414,36 @@
                 <c:pt idx="89">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="90">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4424,6 +4709,48 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="85">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="99">
                   <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
@@ -4600,6 +4927,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4607,7 +4935,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5185,6 +5512,36 @@
                 <c:pt idx="167">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="168">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5684,6 +6041,48 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="163">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="177">
                   <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
@@ -6212,6 +6611,48 @@
                 <c:pt idx="163">
                   <c:v>61</c:v>
                 </c:pt>
+                <c:pt idx="164">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>61</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6736,6 +7177,48 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="163">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="177">
                   <c:v>120</c:v>
                 </c:pt>
               </c:numCache>
@@ -6911,6 +7394,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6918,7 +7402,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9647,15 +10130,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B272F1F1-C221-BA47-B841-D5FD2627A973}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -13667,6 +14150,236 @@
       </c>
       <c r="G169" s="11">
         <v>3.7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C170" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F170" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G170" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C171" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F171" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G171" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C172" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F172" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G172" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C173" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F173" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G173" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F174" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G174" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F175" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G175" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F176" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G176" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F177" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G177" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="F178" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G178" s="11">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F179" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G179" s="11">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -13680,7 +14393,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3EFB630-E0BB-4706-9416-36C816E52A8D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13691,15 +14404,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA8D367-2C3B-E14E-A57E-CFD56EE7448B}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -17634,6 +18347,15 @@
       <c r="D166" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E166" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F166" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G166" s="11">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
@@ -17648,6 +18370,15 @@
       <c r="D167" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E167" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F167" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G167" s="11">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
@@ -17662,6 +18393,15 @@
       <c r="D168" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E168" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F168" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G168" s="11">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
@@ -17675,6 +18415,245 @@
       </c>
       <c r="D169" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E169" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F169" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G169" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C170" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="F170" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="G170" s="11">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C171" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="F171" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="G171" s="11">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C172" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="F172" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="G172" s="11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C173" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="F173" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G173" s="11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="F174" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G174" s="11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="F175" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G175" s="11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="F176" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G176" s="11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="F177" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G177" s="11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="F178" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G178" s="11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="11">
+        <v>6</v>
+      </c>
+      <c r="F179" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="G179" s="11">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17686,15 +18665,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA7DDA5-51A1-B549-8D1A-904152A54486}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -21629,6 +22608,15 @@
       <c r="D166" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E166" s="11">
+        <v>10</v>
+      </c>
+      <c r="F166" s="11">
+        <v>10</v>
+      </c>
+      <c r="G166" s="11">
+        <v>10</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
@@ -21643,6 +22631,15 @@
       <c r="D167" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E167" s="11">
+        <v>10</v>
+      </c>
+      <c r="F167" s="11">
+        <v>10</v>
+      </c>
+      <c r="G167" s="11">
+        <v>10</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
@@ -21657,6 +22654,15 @@
       <c r="D168" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E168" s="11">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="F168" s="11">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G168" s="11">
+        <v>9.6999999999999993</v>
+      </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
@@ -21670,6 +22676,245 @@
       </c>
       <c r="D169" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E169" s="11">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="F169" s="11">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G169" s="11">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C170" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="F170" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G170" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C171" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="F171" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G171" s="11">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C172" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F172" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G172" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C173" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F173" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G173" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F174" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G174" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F175" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G175" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F176" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G176" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F177" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G177" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F178" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G178" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="11">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F179" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G179" s="11">
+        <v>8.6999999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -21681,15 +22926,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DFD583-C049-7E44-B4FF-4B3CC56372E6}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -25624,6 +26869,15 @@
       <c r="D166" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E166" s="11">
+        <v>19</v>
+      </c>
+      <c r="F166" s="11">
+        <v>19</v>
+      </c>
+      <c r="G166" s="11">
+        <v>19</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
@@ -25638,6 +26892,15 @@
       <c r="D167" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E167" s="11">
+        <v>19</v>
+      </c>
+      <c r="F167" s="11">
+        <v>19</v>
+      </c>
+      <c r="G167" s="11">
+        <v>19</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
@@ -25652,6 +26915,15 @@
       <c r="D168" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E168" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="F168" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="G168" s="11">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
@@ -25665,6 +26937,245 @@
       </c>
       <c r="D169" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E169" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="F169" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="G169" s="11">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C170" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="11">
+        <v>18.2</v>
+      </c>
+      <c r="F170" s="11">
+        <v>18.2</v>
+      </c>
+      <c r="G170" s="11">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C171" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="11">
+        <v>18.2</v>
+      </c>
+      <c r="F171" s="11">
+        <v>18.2</v>
+      </c>
+      <c r="G171" s="11">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C172" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="F172" s="11">
+        <v>18.2</v>
+      </c>
+      <c r="G172" s="11">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C173" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="F173" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="G173" s="11">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="F174" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="G174" s="11">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="F175" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="G175" s="11">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="F176" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="G176" s="11">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="F177" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="G177" s="11">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="F178" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="G178" s="11">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="11">
+        <v>16.8</v>
+      </c>
+      <c r="F179" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="G179" s="11">
+        <v>16.8</v>
       </c>
     </row>
   </sheetData>
@@ -25676,15 +27187,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3239D1C2-C3DC-9D47-B02E-5855318CF9C1}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H101"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -27747,6 +29258,15 @@
       <c r="D88" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E88" s="11">
+        <v>42</v>
+      </c>
+      <c r="F88" s="11">
+        <v>42</v>
+      </c>
+      <c r="G88" s="11">
+        <v>42</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
@@ -27761,6 +29281,15 @@
       <c r="D89" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E89" s="11">
+        <v>42</v>
+      </c>
+      <c r="F89" s="11">
+        <v>42</v>
+      </c>
+      <c r="G89" s="11">
+        <v>42</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
@@ -27775,6 +29304,15 @@
       <c r="D90" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E90" s="11">
+        <v>41</v>
+      </c>
+      <c r="F90" s="11">
+        <v>41</v>
+      </c>
+      <c r="G90" s="11">
+        <v>41</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
@@ -27788,6 +29326,245 @@
       </c>
       <c r="D91" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E91" s="11">
+        <v>41</v>
+      </c>
+      <c r="F91" s="11">
+        <v>41</v>
+      </c>
+      <c r="G91" s="11">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B92" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C92" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="11">
+        <v>40</v>
+      </c>
+      <c r="F92" s="11">
+        <v>40</v>
+      </c>
+      <c r="G92" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B93" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C93" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="11">
+        <v>40</v>
+      </c>
+      <c r="F93" s="11">
+        <v>40</v>
+      </c>
+      <c r="G93" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B94" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C94" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="11">
+        <v>39</v>
+      </c>
+      <c r="F94" s="11">
+        <v>40</v>
+      </c>
+      <c r="G94" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B95" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C95" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="11">
+        <v>39</v>
+      </c>
+      <c r="F95" s="11">
+        <v>39</v>
+      </c>
+      <c r="G95" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B96" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C96" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="11">
+        <v>39</v>
+      </c>
+      <c r="F96" s="11">
+        <v>39</v>
+      </c>
+      <c r="G96" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B97" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C97" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="11">
+        <v>39</v>
+      </c>
+      <c r="F97" s="11">
+        <v>39</v>
+      </c>
+      <c r="G97" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B98" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C98" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="11">
+        <v>39</v>
+      </c>
+      <c r="F98" s="11">
+        <v>39</v>
+      </c>
+      <c r="G98" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B99" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C99" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" s="11">
+        <v>39</v>
+      </c>
+      <c r="F99" s="11">
+        <v>39</v>
+      </c>
+      <c r="G99" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B100" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C100" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="11">
+        <v>39</v>
+      </c>
+      <c r="F100" s="11">
+        <v>39</v>
+      </c>
+      <c r="G100" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B101" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C101" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="11">
+        <v>36.5</v>
+      </c>
+      <c r="F101" s="11">
+        <v>39</v>
+      </c>
+      <c r="G101" s="11">
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
@@ -27799,15 +29576,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD2559E0-BF80-8D49-A825-36795DBC5AE8}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:H91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H101"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -29870,6 +31647,15 @@
       <c r="D88" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E88" s="11">
+        <v>24</v>
+      </c>
+      <c r="F88" s="11">
+        <v>24</v>
+      </c>
+      <c r="G88" s="11">
+        <v>24</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
@@ -29884,6 +31670,15 @@
       <c r="D89" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E89" s="11">
+        <v>24</v>
+      </c>
+      <c r="F89" s="11">
+        <v>24</v>
+      </c>
+      <c r="G89" s="11">
+        <v>24</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
@@ -29898,6 +31693,15 @@
       <c r="D90" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E90" s="11">
+        <v>24</v>
+      </c>
+      <c r="F90" s="11">
+        <v>24</v>
+      </c>
+      <c r="G90" s="11">
+        <v>24</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
@@ -29911,6 +31715,245 @@
       </c>
       <c r="D91" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E91" s="11">
+        <v>24</v>
+      </c>
+      <c r="F91" s="11">
+        <v>24</v>
+      </c>
+      <c r="G91" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B92" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C92" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="11">
+        <v>24</v>
+      </c>
+      <c r="F92" s="11">
+        <v>24</v>
+      </c>
+      <c r="G92" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B93" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C93" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="11">
+        <v>24</v>
+      </c>
+      <c r="F93" s="11">
+        <v>24</v>
+      </c>
+      <c r="G93" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B94" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C94" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="11">
+        <v>24</v>
+      </c>
+      <c r="F94" s="11">
+        <v>24</v>
+      </c>
+      <c r="G94" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B95" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C95" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="11">
+        <v>24</v>
+      </c>
+      <c r="F95" s="11">
+        <v>24</v>
+      </c>
+      <c r="G95" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B96" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C96" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="11">
+        <v>24</v>
+      </c>
+      <c r="F96" s="11">
+        <v>24</v>
+      </c>
+      <c r="G96" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B97" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C97" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="11">
+        <v>24</v>
+      </c>
+      <c r="F97" s="11">
+        <v>24</v>
+      </c>
+      <c r="G97" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B98" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C98" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="11">
+        <v>24</v>
+      </c>
+      <c r="F98" s="11">
+        <v>24</v>
+      </c>
+      <c r="G98" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B99" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C99" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" s="11">
+        <v>24</v>
+      </c>
+      <c r="F99" s="11">
+        <v>24</v>
+      </c>
+      <c r="G99" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B100" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C100" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="11">
+        <v>24</v>
+      </c>
+      <c r="F100" s="11">
+        <v>24</v>
+      </c>
+      <c r="G100" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B101" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C101" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="11">
+        <v>24</v>
+      </c>
+      <c r="F101" s="11">
+        <v>24</v>
+      </c>
+      <c r="G101" s="11">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -29922,15 +31965,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9243ABC-FEC6-A34B-8298-85FBF7652B6D}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -33865,6 +35908,15 @@
       <c r="D166" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E166" s="11">
+        <v>33</v>
+      </c>
+      <c r="F166" s="11">
+        <v>33</v>
+      </c>
+      <c r="G166" s="11">
+        <v>33</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
@@ -33879,6 +35931,15 @@
       <c r="D167" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E167" s="11">
+        <v>33</v>
+      </c>
+      <c r="F167" s="11">
+        <v>33</v>
+      </c>
+      <c r="G167" s="11">
+        <v>33</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
@@ -33893,6 +35954,15 @@
       <c r="D168" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E168" s="11">
+        <v>33</v>
+      </c>
+      <c r="F168" s="11">
+        <v>33</v>
+      </c>
+      <c r="G168" s="11">
+        <v>33</v>
+      </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
@@ -33906,6 +35976,245 @@
       </c>
       <c r="D169" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E169" s="11">
+        <v>33</v>
+      </c>
+      <c r="F169" s="11">
+        <v>33</v>
+      </c>
+      <c r="G169" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C170" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="11">
+        <v>33</v>
+      </c>
+      <c r="F170" s="11">
+        <v>33</v>
+      </c>
+      <c r="G170" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C171" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="11">
+        <v>33</v>
+      </c>
+      <c r="F171" s="11">
+        <v>33</v>
+      </c>
+      <c r="G171" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C172" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="11">
+        <v>33</v>
+      </c>
+      <c r="F172" s="11">
+        <v>33</v>
+      </c>
+      <c r="G172" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C173" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="11">
+        <v>33</v>
+      </c>
+      <c r="F173" s="11">
+        <v>33</v>
+      </c>
+      <c r="G173" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="11">
+        <v>33</v>
+      </c>
+      <c r="F174" s="11">
+        <v>33</v>
+      </c>
+      <c r="G174" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="11">
+        <v>33</v>
+      </c>
+      <c r="F175" s="11">
+        <v>33</v>
+      </c>
+      <c r="G175" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>33</v>
+      </c>
+      <c r="F176" s="11">
+        <v>33</v>
+      </c>
+      <c r="G176" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="11">
+        <v>33</v>
+      </c>
+      <c r="F177" s="11">
+        <v>33</v>
+      </c>
+      <c r="G177" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="11">
+        <v>33</v>
+      </c>
+      <c r="F178" s="11">
+        <v>33</v>
+      </c>
+      <c r="G178" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="11">
+        <v>33</v>
+      </c>
+      <c r="F179" s="11">
+        <v>33</v>
+      </c>
+      <c r="G179" s="11">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -33917,15 +36226,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFF5017-E975-3245-B813-D752FBEC2974}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -37860,6 +40169,15 @@
       <c r="D166" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E166" s="11">
+        <v>61</v>
+      </c>
+      <c r="F166" s="11">
+        <v>61</v>
+      </c>
+      <c r="G166" s="11">
+        <v>61</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
@@ -37874,6 +40192,15 @@
       <c r="D167" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E167" s="11">
+        <v>61</v>
+      </c>
+      <c r="F167" s="11">
+        <v>61</v>
+      </c>
+      <c r="G167" s="11">
+        <v>61</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
@@ -37888,6 +40215,15 @@
       <c r="D168" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E168" s="11">
+        <v>61</v>
+      </c>
+      <c r="F168" s="11">
+        <v>61</v>
+      </c>
+      <c r="G168" s="11">
+        <v>61</v>
+      </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
@@ -37901,6 +40237,245 @@
       </c>
       <c r="D169" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E169" s="11">
+        <v>61</v>
+      </c>
+      <c r="F169" s="11">
+        <v>61</v>
+      </c>
+      <c r="G169" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C170" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="11">
+        <v>61</v>
+      </c>
+      <c r="F170" s="11">
+        <v>61</v>
+      </c>
+      <c r="G170" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C171" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="11">
+        <v>61</v>
+      </c>
+      <c r="F171" s="11">
+        <v>61</v>
+      </c>
+      <c r="G171" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C172" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="11">
+        <v>61</v>
+      </c>
+      <c r="F172" s="11">
+        <v>61</v>
+      </c>
+      <c r="G172" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C173" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="11">
+        <v>61</v>
+      </c>
+      <c r="F173" s="11">
+        <v>61</v>
+      </c>
+      <c r="G173" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="11">
+        <v>61</v>
+      </c>
+      <c r="F174" s="11">
+        <v>61</v>
+      </c>
+      <c r="G174" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="11">
+        <v>61</v>
+      </c>
+      <c r="F175" s="11">
+        <v>61</v>
+      </c>
+      <c r="G175" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>61</v>
+      </c>
+      <c r="F176" s="11">
+        <v>61</v>
+      </c>
+      <c r="G176" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="11">
+        <v>61</v>
+      </c>
+      <c r="F177" s="11">
+        <v>61</v>
+      </c>
+      <c r="G177" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="11">
+        <v>61</v>
+      </c>
+      <c r="F178" s="11">
+        <v>61</v>
+      </c>
+      <c r="G178" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="11">
+        <v>61</v>
+      </c>
+      <c r="F179" s="11">
+        <v>61</v>
+      </c>
+      <c r="G179" s="11">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -37912,15 +40487,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E7EEF0-A0B2-3A49-9389-9D8B09E58931}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -41855,6 +44430,15 @@
       <c r="D166" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E166" s="11">
+        <v>120</v>
+      </c>
+      <c r="F166" s="11">
+        <v>120</v>
+      </c>
+      <c r="G166" s="11">
+        <v>120</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
@@ -41869,6 +44453,15 @@
       <c r="D167" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E167" s="11">
+        <v>120</v>
+      </c>
+      <c r="F167" s="11">
+        <v>120</v>
+      </c>
+      <c r="G167" s="11">
+        <v>120</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
@@ -41883,6 +44476,15 @@
       <c r="D168" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="E168" s="11">
+        <v>120</v>
+      </c>
+      <c r="F168" s="11">
+        <v>120</v>
+      </c>
+      <c r="G168" s="11">
+        <v>120</v>
+      </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
@@ -41896,6 +44498,245 @@
       </c>
       <c r="D169" s="7" t="s">
         <v>8</v>
+      </c>
+      <c r="E169" s="11">
+        <v>120</v>
+      </c>
+      <c r="F169" s="11">
+        <v>120</v>
+      </c>
+      <c r="G169" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46122</v>
+      </c>
+      <c r="C170" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="11">
+        <v>120</v>
+      </c>
+      <c r="F170" s="11">
+        <v>120</v>
+      </c>
+      <c r="G170" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C171" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="11">
+        <v>120</v>
+      </c>
+      <c r="F171" s="11">
+        <v>120</v>
+      </c>
+      <c r="G171" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C172" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="11">
+        <v>120</v>
+      </c>
+      <c r="F172" s="11">
+        <v>120</v>
+      </c>
+      <c r="G172" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46127</v>
+      </c>
+      <c r="C173" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="11">
+        <v>120</v>
+      </c>
+      <c r="F173" s="11">
+        <v>120</v>
+      </c>
+      <c r="G173" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="11">
+        <v>120</v>
+      </c>
+      <c r="F174" s="11">
+        <v>120</v>
+      </c>
+      <c r="G174" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46129</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="11">
+        <v>120</v>
+      </c>
+      <c r="F175" s="11">
+        <v>120</v>
+      </c>
+      <c r="G175" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="11">
+        <v>120</v>
+      </c>
+      <c r="F176" s="11">
+        <v>120</v>
+      </c>
+      <c r="G176" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="11">
+        <v>120</v>
+      </c>
+      <c r="F177" s="11">
+        <v>120</v>
+      </c>
+      <c r="G177" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46134</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="11">
+        <v>120</v>
+      </c>
+      <c r="F178" s="11">
+        <v>120</v>
+      </c>
+      <c r="G178" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="11">
+        <v>120</v>
+      </c>
+      <c r="F179" s="11">
+        <v>120</v>
+      </c>
+      <c r="G179" s="11">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
